--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117866380</v>
+        <v>118719297</v>
       </c>
       <c r="B2" t="n">
-        <v>90503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Laxsjön, Mpd</t>
+          <t>Laxsjön, ca 1 km NV byn, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610558</v>
+        <v>610530</v>
       </c>
       <c r="R2" t="n">
-        <v>6966830</v>
+        <v>6966881</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,30 +757,38 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>gammal barrskog med gott om död ved</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # mycket grov förrötad granlåga, marknära</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117866381</v>
+        <v>117866380</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610520</v>
+        <v>610558</v>
       </c>
       <c r="R3" t="n">
-        <v>6966938</v>
+        <v>6966830</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +859,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +869,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118719297</v>
+        <v>117866381</v>
       </c>
       <c r="B4" t="n">
-        <v>90460</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +907,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Laxsjön, ca 1 km NV byn, Mpd</t>
+          <t>Laxsjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610530</v>
+        <v>610520</v>
       </c>
       <c r="R4" t="n">
-        <v>6966881</v>
+        <v>6966938</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,12 +965,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,78 +992,72 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>gammal barrskog med gott om död ved</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter # mycket grov förrötad granlåga, marknära</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118719298</v>
+        <v>89789170</v>
       </c>
       <c r="B5" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>102125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laxsjön, ca 1 km NV byn, Mpd</t>
+          <t>Laxsjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610506</v>
+        <v>610452</v>
       </c>
       <c r="R5" t="n">
-        <v>6966919</v>
+        <v>6967029</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,12 +1084,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2020-12-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2020-12-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,28 +1101,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre barrblandskog med inslag av gammal gran</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov granhögstubbe</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Mattias Edman, Assar Edman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 52150-2025 artfynd.xlsx
+++ b/artfynd/A 52150-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118719297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117866380</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117866381</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,8 +1133,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89789170</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>